--- a/docs/독서기록앱_테이블정의서.xlsx
+++ b/docs/독서기록앱_테이블정의서.xlsx
@@ -54,7 +54,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +123,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -485,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -504,7 +515,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기획서 5. 데이터 모델 기반 / 작성일: 2026-07-01 · 수정일: 2026-07-03 (화면설계서 v2 반영)</t>
+          <t>기획서 5. 데이터 모델 기반 / 작성일: 2026-07-01 · 수정일: 2026-07-21 (Step 5/5-2 반영: ShareRecord.user_id/book_note_id/dashboard_snapshot 컬럼, ShareRecordPhoto 테이블 추가)</t>
         </is>
       </c>
     </row>
@@ -754,6 +765,28 @@
       <c r="D15" s="6" t="inlineStr">
         <is>
           <t>공유 탭</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>ShareRecordPhoto</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>공유 사진</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>공유 시 선택한 사진(N장, 순서 포함) 매핑</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>공유 탭, 마이페이지(Recap)</t>
         </is>
       </c>
     </row>
@@ -768,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2647,68 +2680,72 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>ShareRecord</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>User.id</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>공유한 사용자 (dashboard 공유는 book_id가 없어 공유자 식별을 위해 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>ShareRecord</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>share_type</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(20)</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="inlineStr"/>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr"/>
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>book(독서기록 공유) / dashboard(대시보드 공유)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>ShareRecord</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr"/>
-      <c r="F52" s="6" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>all(전체공개) / group(그룹) / custom(인원지정)</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2760,12 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr"/>
@@ -2741,44 +2778,40 @@
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
+          <t>all(전체공개) / group(그룹) / custom(인원지정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>ShareRecord</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
           <t>app / instagram / threads / tiktok</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>ShareRecord</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>card_image_url</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR(255)</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>생성된 공유 카드 이미지 URL (S3)</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2826,12 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>public_token</t>
+          <t>card_image_url</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr"/>
@@ -2815,122 +2848,122 @@
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
+          <t>생성된 공유 카드 이미지 URL (S3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>ShareRecord</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>public_token</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
           <t>비로그인 공개 웹뷰 접근용 UUID 토큰</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>ShareRecord</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>shared_at</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr"/>
-      <c r="F56" s="6" t="inlineStr"/>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>공유 일시</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>ShareRecordTarget</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>book_note_id</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>BIGINT</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>BookNote.id</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr"/>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>AUTO_INCREMENT</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>공유 대상 고유 ID</t>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>카드/공개 페이지에 노출할 소감 (share_type=book이고 사용자가 선택했을 때만 값 있음)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="n">
+      <c r="A58" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>ShareRecordTarget</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>share_record_id</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr"/>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>ShareRecord.id</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>소속 공유 기록</t>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>ShareRecord</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>dashboard_snapshot</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>share_type=dashboard일 때 공유 시점의 대시보드 통계(JSON)를 그대로 얼려서 저장</t>
         </is>
       </c>
     </row>
@@ -2940,17 +2973,17 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>ShareRecordTarget</t>
+          <t>ShareRecord</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>target_type</t>
+          <t>shared_at</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr"/>
@@ -2960,10 +2993,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>user(개인) / group(그룹)</t>
+          <t>공유 일시</t>
         </is>
       </c>
     </row>
@@ -2978,29 +3015,288 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>공유 대상 고유 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>ShareRecordTarget</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>share_record_id</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>ShareRecord.id</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>소속 공유 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>ShareRecordTarget</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>target_type</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr"/>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>user(개인) / group(그룹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>ShareRecordTarget</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>BIGINT</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr"/>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>User.id / Group.id</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>target_type에 따라 User 또는 Group 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>ShareRecordPhoto</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="n"/>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>공유 사진 매핑 고유 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>ShareRecordPhoto</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>share_record_id</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>ShareRecord.id</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>소속 공유 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>ShareRecordPhoto</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>book_photo_id</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>BookPhoto.id</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>공유 시 선택한 사진</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>ShareRecordPhoto</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>display_order</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>노출 순서 (0부터, share_record_id+book_photo_id 유니크)</t>
         </is>
       </c>
     </row>
